--- a/nuevas_campañas_errado.xlsx
+++ b/nuevas_campañas_errado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,33 +452,40 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1 VTA-PR</t>
+          <t>2 VTA-PR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4 VTA PR</t>
+          <t>1 VTA-PR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2 VTA-PR</t>
+          <t>4 VTA-PR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4 VTA-PR</t>
+          <t>4 VTA - PR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
+        <is>
+          <t>4 VTA PR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>3 VTA-PR</t>
         </is>
